--- a/examples/福耀玻璃.xlsx
+++ b/examples/福耀玻璃.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21600" activeTab="1"/>
+    <workbookView windowWidth="21600" windowHeight="32460" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="balance" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="223">
   <si>
     <t>2024.12.31</t>
   </si>
@@ -83,7 +83,7 @@
     <t>其他流动资产</t>
   </si>
   <si>
-    <t>长期股权资产</t>
+    <t>长期投资资产</t>
   </si>
   <si>
     <t>长期股权投资</t>
@@ -470,22 +470,34 @@
     <t>主营业务</t>
   </si>
   <si>
+    <t>主营业务收入</t>
+  </si>
+  <si>
+    <t>汽车玻璃</t>
+  </si>
+  <si>
+    <t>浮法玻璃</t>
+  </si>
+  <si>
+    <t>毛利</t>
+  </si>
+  <si>
+    <t>其他业务</t>
+  </si>
+  <si>
+    <t>其他业务收入</t>
+  </si>
+  <si>
+    <t>其他业务成本</t>
+  </si>
+  <si>
+    <t>其他业务毛利</t>
+  </si>
+  <si>
+    <t>YoY</t>
+  </si>
+  <si>
     <t>收入</t>
-  </si>
-  <si>
-    <t>汽车玻璃</t>
-  </si>
-  <si>
-    <t>浮法玻璃</t>
-  </si>
-  <si>
-    <t>毛利</t>
-  </si>
-  <si>
-    <t>其他业务</t>
-  </si>
-  <si>
-    <t>YoY</t>
   </si>
   <si>
     <t>定价</t>
@@ -706,7 +718,7 @@
     <numFmt numFmtId="181" formatCode="0.0"/>
     <numFmt numFmtId="182" formatCode="#,##0_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -717,13 +729,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <charset val="134"/>
@@ -901,7 +906,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1084,12 +1089,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1212,13 +1211,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1227,13 +1226,16 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1242,122 +1244,119 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1376,19 +1375,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1397,13 +1396,13 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
@@ -1421,13 +1420,13 @@
     <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -1442,7 +1441,7 @@
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
@@ -1451,16 +1450,16 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1472,22 +1471,22 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -1496,16 +1495,16 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1">
@@ -1514,10 +1513,10 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -1526,26 +1525,23 @@
     <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3378,16 +3374,16 @@
       <c r="D50" s="56">
         <v>5413589161</v>
       </c>
-      <c r="E50" s="62">
+      <c r="E50" s="3">
         <v>6076527372</v>
       </c>
-      <c r="F50" s="62">
+      <c r="F50" s="3">
         <v>5925550792</v>
       </c>
-      <c r="G50" s="62">
+      <c r="G50" s="3">
         <v>6165804499</v>
       </c>
-      <c r="H50" s="62">
+      <c r="H50" s="3">
         <v>8491599785</v>
       </c>
       <c r="I50" s="49">
@@ -3413,16 +3409,16 @@
       <c r="D51" s="56">
         <v>8513100000</v>
       </c>
-      <c r="E51" s="62">
+      <c r="E51" s="3">
         <v>3007000000</v>
       </c>
-      <c r="F51" s="62">
+      <c r="F51" s="3">
         <v>1138940000</v>
       </c>
-      <c r="G51" s="62">
+      <c r="G51" s="3">
         <v>1985000000</v>
       </c>
-      <c r="H51" s="62">
+      <c r="H51" s="3">
         <v>1193000000</v>
       </c>
       <c r="I51" s="49">
@@ -3444,12 +3440,12 @@
       </c>
       <c r="C52" s="54"/>
       <c r="D52" s="56"/>
-      <c r="E52" s="62"/>
-      <c r="F52" s="62"/>
-      <c r="G52" s="62">
+      <c r="E52" s="3"/>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3">
         <v>795244</v>
       </c>
-      <c r="H52" s="62">
+      <c r="H52" s="3">
         <v>3795000</v>
       </c>
       <c r="I52" s="49">
@@ -3468,11 +3464,11 @@
       </c>
       <c r="C53" s="56"/>
       <c r="D53" s="56"/>
-      <c r="E53" s="62"/>
-      <c r="F53" s="62">
+      <c r="E53" s="3"/>
+      <c r="F53" s="3">
         <v>1198778297</v>
       </c>
-      <c r="G53" s="62">
+      <c r="G53" s="3">
         <v>1198784928</v>
       </c>
       <c r="H53" s="60"/>
@@ -3489,9 +3485,9 @@
       </c>
       <c r="C54" s="56"/>
       <c r="D54" s="56"/>
-      <c r="E54" s="62"/>
-      <c r="F54" s="62"/>
-      <c r="G54" s="62"/>
+      <c r="E54" s="3"/>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
       <c r="H54" s="60"/>
       <c r="J54" s="49"/>
       <c r="K54" s="49">
@@ -3534,10 +3530,10 @@
       <c r="D56" s="56">
         <v>202102553</v>
       </c>
-      <c r="E56" s="62">
+      <c r="E56" s="3">
         <v>2145153663</v>
       </c>
-      <c r="F56" s="62">
+      <c r="F56" s="3">
         <v>1627919125</v>
       </c>
       <c r="G56" s="3">
@@ -3569,10 +3565,10 @@
       <c r="D57" s="56">
         <v>407132248</v>
       </c>
-      <c r="E57" s="62">
+      <c r="E57" s="3">
         <v>476982049</v>
       </c>
-      <c r="F57" s="62">
+      <c r="F57" s="3">
         <v>507683371</v>
       </c>
       <c r="G57" s="3">
@@ -3583,8 +3579,8 @@
       </c>
     </row>
     <row r="58" spans="1:12">
-      <c r="E58" s="62"/>
-      <c r="F58" s="62"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
     </row>
@@ -7064,7 +7060,7 @@
     </row>
     <row r="17" s="13" customFormat="1" spans="1:11">
       <c r="A17" s="23" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B17" s="41">
         <v>541228588</v>
@@ -7099,7 +7095,7 @@
     </row>
     <row r="18" s="13" customFormat="1" spans="1:11">
       <c r="A18" s="23" t="s">
-        <v>71</v>
+        <v>152</v>
       </c>
       <c r="B18" s="41">
         <v>108449502</v>
@@ -7134,7 +7130,7 @@
     </row>
     <row r="19" s="13" customFormat="1" spans="1:11">
       <c r="A19" s="23" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B19" s="41">
         <f>B17-B18</f>
@@ -7179,12 +7175,12 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="40" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B23" s="12">
         <f>B3/C3-1</f>
@@ -7343,10 +7339,10 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="17" customHeight="1" spans="1:13">
       <c r="B1" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D1" s="1">
         <v>2024</v>
@@ -7426,7 +7422,7 @@
     </row>
     <row r="3" spans="1:13">
       <c r="A3" s="4" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="D3" s="3">
         <f>balance!C4</f>
@@ -7471,7 +7467,7 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="4" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D4" s="3">
         <f>balance!C10</f>
@@ -7516,7 +7512,7 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="4" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D5" s="3">
         <f>balance!C13</f>
@@ -7561,7 +7557,7 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D6" s="3">
         <f>balance!C15+balance!C16</f>
@@ -7606,7 +7602,7 @@
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="6" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="D7" s="3">
         <f>balance!C17</f>
@@ -7786,7 +7782,7 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="7" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D11" s="3">
         <f>balance!C39+balance!C38</f>
@@ -7831,7 +7827,7 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="4" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D12" s="3">
         <f>balance!C36+balance!C37</f>
@@ -7921,7 +7917,7 @@
     </row>
     <row r="14" ht="17.6" spans="1:13">
       <c r="A14" s="2" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B14" s="8"/>
       <c r="C14" s="8"/>
@@ -7968,7 +7964,7 @@
     </row>
     <row r="15" ht="17.6" spans="1:13">
       <c r="A15" s="9" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D15" s="3">
         <f>balance!C61+balance!C62</f>
@@ -8058,7 +8054,7 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="10" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D17" s="3">
         <f>balance!C71</f>
@@ -8115,7 +8111,7 @@
     </row>
     <row r="19" ht="17.6" spans="1:13">
       <c r="A19" s="11" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="D19" s="3">
         <f t="shared" ref="D19:M19" si="0">D3</f>
@@ -8160,7 +8156,7 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="5" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D20" s="3">
         <f t="shared" ref="D20:M20" si="1">D16</f>
@@ -8205,7 +8201,7 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D21" s="3">
         <f>D19-D20</f>
@@ -8262,7 +8258,7 @@
     </row>
     <row r="23" ht="17.6" spans="1:13">
       <c r="A23" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D23" s="3">
         <f>SUM(损益现金流!B38:B41)</f>
@@ -8307,7 +8303,7 @@
     </row>
     <row r="24" ht="17.6" spans="1:13">
       <c r="A24" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D24" s="3">
         <f>损益现金流!B72</f>
@@ -8365,7 +8361,7 @@
     </row>
     <row r="26" ht="17.6" spans="1:13">
       <c r="A26" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B26" s="8">
         <f>D26</f>
@@ -8431,7 +8427,7 @@
     </row>
     <row r="28" ht="17.6" spans="1:13">
       <c r="A28" s="11" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D28" s="3">
         <f>收入成本!B3</f>
@@ -8476,7 +8472,7 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="4" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D29" s="3">
         <f>收入成本!B8</f>
@@ -8521,7 +8517,7 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="4" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D30" s="3">
         <f>SUM(损益现金流!B5:B8)</f>
@@ -8701,7 +8697,7 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D34" s="3">
         <f>SUM(损益现金流!B11:B13)</f>
@@ -8791,7 +8787,7 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="10" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D36" s="3">
         <f>损益现金流!B20</f>
@@ -8836,7 +8832,7 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="10" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D37" s="3">
         <f>损益现金流!B25</f>
@@ -8986,7 +8982,7 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="4" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="D41" s="3">
         <f>收入成本!B17</f>
@@ -9076,7 +9072,7 @@
     </row>
     <row r="43" ht="17.6" spans="1:13">
       <c r="A43" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -9091,7 +9087,7 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="4" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="D44" s="3">
         <f>损益现金流!B15</f>
@@ -9252,7 +9248,7 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="13" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="12"/>
@@ -9267,7 +9263,7 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="15" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
@@ -9314,7 +9310,7 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="D51" s="8">
         <f>D29</f>
@@ -9359,7 +9355,7 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="5" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D52" s="18">
         <f>D30</f>
@@ -9404,7 +9400,7 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="5" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D53" s="18">
         <f>D34</f>
@@ -9494,7 +9490,7 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="5" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D55" s="18">
         <f>D36</f>
@@ -9674,7 +9670,7 @@
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="15" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B59" s="19">
         <f>D59*1.3</f>
@@ -9727,7 +9723,7 @@
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="5" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D60" s="8">
         <f>D37</f>
@@ -9772,7 +9768,7 @@
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="5" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D61" s="8">
         <f>D41-D42</f>
@@ -9817,7 +9813,7 @@
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D62" s="8">
         <f>D44-D45</f>
@@ -9952,7 +9948,7 @@
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="15" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
@@ -9999,7 +9995,7 @@
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D66" s="8">
         <f>D23</f>
@@ -10044,7 +10040,7 @@
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="5" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="D67" s="8">
         <f>D24</f>
@@ -10089,7 +10085,7 @@
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="15" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B68" s="16"/>
       <c r="C68" s="16"/>
@@ -10136,7 +10132,7 @@
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="15" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B69" s="16"/>
       <c r="C69" s="16"/>
@@ -10196,7 +10192,7 @@
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="10" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D71" s="22"/>
       <c r="E71" s="22"/>
@@ -10256,7 +10252,7 @@
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="23" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D73" s="22">
         <f>D30/D28</f>
@@ -10301,7 +10297,7 @@
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="23" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="D74" s="22">
         <f>D31/D28</f>
@@ -10346,7 +10342,7 @@
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="23" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D75" s="22">
         <f>D32/D28</f>
@@ -10391,7 +10387,7 @@
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="23" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D76" s="22">
         <f>D33/D28</f>
@@ -10436,7 +10432,7 @@
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="23" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D77" s="22">
         <f>D59/D28</f>
@@ -10494,7 +10490,7 @@
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="23" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D79" s="22">
         <f>D6/D28</f>
@@ -10539,7 +10535,7 @@
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="23" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="D80" s="8">
         <f>D28/D6</f>
@@ -10584,7 +10580,7 @@
     </row>
     <row r="81" spans="1:13">
       <c r="A81" s="23" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="D81" s="24">
         <f>D29/D8</f>
@@ -10629,7 +10625,7 @@
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="23" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="D82" s="22">
         <f>(D12-D7)/D29</f>
@@ -10674,7 +10670,7 @@
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="23" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="D83" s="12">
         <f>D11/D28</f>
@@ -10719,7 +10715,7 @@
     </row>
     <row r="84" spans="1:13">
       <c r="A84" s="23" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D84" s="22">
         <f>D56/D59</f>
@@ -10764,7 +10760,7 @@
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="23" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D85" s="22">
         <f>D23/D9</f>
@@ -10822,7 +10818,7 @@
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="10" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="D87" s="12"/>
       <c r="E87" s="12"/>
@@ -10837,7 +10833,7 @@
     </row>
     <row r="88" spans="1:13">
       <c r="A88" s="23" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="D88" s="12">
         <f>D3/D2</f>
@@ -10882,7 +10878,7 @@
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="23" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="D89" s="12">
         <f>D4/D2</f>
@@ -11017,7 +11013,7 @@
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="10" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D92" s="22"/>
       <c r="E92" s="22"/>
@@ -11126,7 +11122,7 @@
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="10" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B95" s="26"/>
       <c r="C95" s="27"/>
@@ -11143,7 +11139,7 @@
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="23" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B96" s="22"/>
       <c r="C96" s="22"/>
@@ -11190,7 +11186,7 @@
     </row>
     <row r="97" spans="1:13">
       <c r="A97" s="23" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D97" s="22">
         <f>D16/D2</f>
@@ -11248,7 +11244,7 @@
     </row>
     <row r="99" spans="1:13">
       <c r="A99" s="28" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B99" s="16"/>
       <c r="C99" s="16"/>
@@ -11292,7 +11288,7 @@
     </row>
     <row r="100" spans="1:13">
       <c r="A100" s="28" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B100" s="16"/>
       <c r="C100" s="16"/>
@@ -11347,7 +11343,7 @@
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="13" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="D102" s="22">
         <f>D2/E2-1</f>
@@ -11389,7 +11385,7 @@
     </row>
     <row r="103" spans="1:13">
       <c r="A103" s="6" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B103" s="30"/>
       <c r="C103" s="30"/>
@@ -11433,7 +11429,7 @@
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="6" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B104" s="30"/>
       <c r="C104" s="30"/>
@@ -11477,7 +11473,7 @@
     </row>
     <row r="105" spans="1:13">
       <c r="A105" s="6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D105" s="22">
         <f>(D5-E5)/(D2-E2)*D102</f>
@@ -11561,7 +11557,7 @@
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="13" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="D107" s="22">
         <f>D14/E14-1</f>
@@ -11603,7 +11599,7 @@
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="6" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="D108" s="25">
         <f>(D15-E15)/(D14-E14)*D107</f>
@@ -11687,7 +11683,7 @@
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="13" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="D110" s="25">
         <f>D10/E10-1</f>
@@ -11729,7 +11725,7 @@
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="6" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="D111" s="25">
         <f>(D11-E11)/(D10-E10)*D110</f>
@@ -11771,7 +11767,7 @@
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="6" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D112" s="31">
         <f>(D12-E12)/(D10-E10)*D110</f>
@@ -11813,7 +11809,7 @@
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="6" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="D113" s="31">
         <f>(D13-E13)/(D10-E10)*D110</f>
@@ -11859,7 +11855,7 @@
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="33" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B115" s="29"/>
       <c r="C115" s="29"/>
@@ -11906,7 +11902,7 @@
     </row>
     <row r="116" ht="17.6" spans="1:13">
       <c r="A116" s="34" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B116" s="29"/>
       <c r="C116" s="29"/>
@@ -11953,7 +11949,7 @@
     </row>
     <row r="117" spans="1:13">
       <c r="A117" s="35" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B117" s="36"/>
       <c r="C117" s="36"/>
@@ -12000,7 +11996,7 @@
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="35" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B118" s="36"/>
       <c r="C118" s="36"/>
@@ -12060,7 +12056,7 @@
     </row>
     <row r="120" spans="1:13">
       <c r="A120" s="33" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B120" s="36">
         <f t="shared" ref="B120:D120" si="62">B64/B26</f>
@@ -12113,7 +12109,7 @@
     </row>
     <row r="121" ht="17.6" spans="1:13">
       <c r="A121" s="37" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B121" s="36">
         <f t="shared" ref="B121:D121" si="64">B59/B26</f>
@@ -12166,7 +12162,7 @@
     </row>
     <row r="122" ht="17.6" spans="1:13">
       <c r="A122" s="37" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B122" s="36">
         <f t="shared" ref="B122:D122" si="66">B69/B26</f>
@@ -12222,7 +12218,7 @@
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="13" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B124">
         <v>57</v>
@@ -12263,7 +12259,7 @@
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="13" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B125">
         <v>64.8</v>
@@ -12304,7 +12300,7 @@
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="13" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B126" s="32">
         <f t="shared" ref="B126:C126" si="68">B124/B121</f>
@@ -12357,7 +12353,7 @@
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="13" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B127" s="32">
         <f t="shared" ref="B127:C127" si="70">B125/B121</f>
@@ -12410,7 +12406,7 @@
     </row>
     <row r="128" spans="1:13">
       <c r="A128" s="13" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B128" s="39">
         <f t="shared" ref="B128:C128" si="72">B120/B124</f>
@@ -12463,7 +12459,7 @@
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="13" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B129" s="39">
         <f t="shared" ref="B129:C129" si="74">B120/B125</f>
@@ -12516,7 +12512,7 @@
     </row>
     <row r="132" spans="1:13">
       <c r="A132" s="13" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B132" s="8">
         <f t="shared" ref="B132:D132" si="76">B124*B26</f>
@@ -12569,7 +12565,7 @@
     </row>
     <row r="133" spans="1:13">
       <c r="A133" s="13" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="B133" s="8">
         <f t="shared" ref="B133:D133" si="78">B125*B26</f>
